--- a/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
+++ b/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
@@ -9687,7 +9687,9 @@
       <c r="PV8" t="n">
         <v>61.24</v>
       </c>
-      <c r="PW8" t="inlineStr"/>
+      <c r="PW8" t="n">
+        <v>60.99</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10894,7 +10896,9 @@
       <c r="PV9" t="n">
         <v>7.05</v>
       </c>
-      <c r="PW9" t="inlineStr"/>
+      <c r="PW9" t="n">
+        <v>6.23</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -12101,7 +12105,9 @@
       <c r="PV10" t="n">
         <v>0.06</v>
       </c>
-      <c r="PW10" t="inlineStr"/>
+      <c r="PW10" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13308,7 +13314,9 @@
       <c r="PV11" t="n">
         <v>0.61</v>
       </c>
-      <c r="PW11" t="inlineStr"/>
+      <c r="PW11" t="n">
+        <v>0.57</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -15050,7 +15058,9 @@
       <c r="PV13" t="n">
         <v>24.01</v>
       </c>
-      <c r="PW13" t="inlineStr"/>
+      <c r="PW13" t="n">
+        <v>28.28</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -16257,7 +16267,9 @@
       <c r="PV14" t="n">
         <v>3.25</v>
       </c>
-      <c r="PW14" t="inlineStr"/>
+      <c r="PW14" t="n">
+        <v>3.67</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17464,7 +17476,9 @@
       <c r="PV15" t="n">
         <v>21.96</v>
       </c>
-      <c r="PW15" t="inlineStr"/>
+      <c r="PW15" t="n">
+        <v>22.92</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
+++ b/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PW15"/>
+  <dimension ref="A1:PX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2605,6 +2605,11 @@
       <c r="PW1" t="inlineStr">
         <is>
           <t>2026-01</t>
+        </is>
+      </c>
+      <c r="PX1" t="inlineStr">
+        <is>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -3816,6 +3821,9 @@
       <c r="PW2" t="n">
         <v>4.35</v>
       </c>
+      <c r="PX2" t="n">
+        <v>4.27</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5025,6 +5033,9 @@
       <c r="PW3" t="n">
         <v>314.51</v>
       </c>
+      <c r="PX3" t="n">
+        <v>295.75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6233,6 +6244,9 @@
       </c>
       <c r="PW4" t="n">
         <v>3.53</v>
+      </c>
+      <c r="PX4" t="n">
+        <v>3.48</v>
       </c>
     </row>
     <row r="5">
@@ -6983,6 +6997,7 @@
       <c r="PU5" t="inlineStr"/>
       <c r="PV5" t="inlineStr"/>
       <c r="PW5" t="inlineStr"/>
+      <c r="PX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7732,6 +7747,7 @@
       <c r="PU6" t="inlineStr"/>
       <c r="PV6" t="inlineStr"/>
       <c r="PW6" t="inlineStr"/>
+      <c r="PX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8481,6 +8497,7 @@
       <c r="PU7" t="inlineStr"/>
       <c r="PV7" t="inlineStr"/>
       <c r="PW7" t="inlineStr"/>
+      <c r="PX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -9690,6 +9707,7 @@
       <c r="PW8" t="n">
         <v>60.99</v>
       </c>
+      <c r="PX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10899,6 +10917,7 @@
       <c r="PW9" t="n">
         <v>6.23</v>
       </c>
+      <c r="PX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -12108,6 +12127,7 @@
       <c r="PW10" t="n">
         <v>0.11</v>
       </c>
+      <c r="PX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13317,6 +13337,7 @@
       <c r="PW11" t="n">
         <v>0.57</v>
       </c>
+      <c r="PX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13900,6 +13921,7 @@
       <c r="PU12" t="inlineStr"/>
       <c r="PV12" t="inlineStr"/>
       <c r="PW12" t="inlineStr"/>
+      <c r="PX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15061,6 +15083,7 @@
       <c r="PW13" t="n">
         <v>28.28</v>
       </c>
+      <c r="PX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -16270,6 +16293,7 @@
       <c r="PW14" t="n">
         <v>3.67</v>
       </c>
+      <c r="PX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17479,6 +17503,7 @@
       <c r="PW15" t="n">
         <v>22.92</v>
       </c>
+      <c r="PX15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
+++ b/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PX15"/>
+  <dimension ref="A1:PY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2610,6 +2610,11 @@
       <c r="PX1" t="inlineStr">
         <is>
           <t>2026-02</t>
+        </is>
+      </c>
+      <c r="PY1" t="inlineStr">
+        <is>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -3824,6 +3829,7 @@
       <c r="PX2" t="n">
         <v>4.27</v>
       </c>
+      <c r="PY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5036,6 +5042,7 @@
       <c r="PX3" t="n">
         <v>295.75</v>
       </c>
+      <c r="PY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6248,6 +6255,7 @@
       <c r="PX4" t="n">
         <v>3.48</v>
       </c>
+      <c r="PY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -6998,6 +7006,7 @@
       <c r="PV5" t="inlineStr"/>
       <c r="PW5" t="inlineStr"/>
       <c r="PX5" t="inlineStr"/>
+      <c r="PY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7748,6 +7757,7 @@
       <c r="PV6" t="inlineStr"/>
       <c r="PW6" t="inlineStr"/>
       <c r="PX6" t="inlineStr"/>
+      <c r="PY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8498,6 +8508,7 @@
       <c r="PV7" t="inlineStr"/>
       <c r="PW7" t="inlineStr"/>
       <c r="PX7" t="inlineStr"/>
+      <c r="PY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -9708,6 +9719,7 @@
         <v>60.99</v>
       </c>
       <c r="PX8" t="inlineStr"/>
+      <c r="PY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10918,6 +10930,7 @@
         <v>6.23</v>
       </c>
       <c r="PX9" t="inlineStr"/>
+      <c r="PY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -12128,6 +12141,7 @@
         <v>0.11</v>
       </c>
       <c r="PX10" t="inlineStr"/>
+      <c r="PY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13338,6 +13352,7 @@
         <v>0.57</v>
       </c>
       <c r="PX11" t="inlineStr"/>
+      <c r="PY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13922,6 +13937,7 @@
       <c r="PV12" t="inlineStr"/>
       <c r="PW12" t="inlineStr"/>
       <c r="PX12" t="inlineStr"/>
+      <c r="PY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15084,6 +15100,7 @@
         <v>28.28</v>
       </c>
       <c r="PX13" t="inlineStr"/>
+      <c r="PY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -16294,6 +16311,7 @@
         <v>3.67</v>
       </c>
       <c r="PX14" t="inlineStr"/>
+      <c r="PY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17504,6 +17522,7 @@
         <v>22.92</v>
       </c>
       <c r="PX15" t="inlineStr"/>
+      <c r="PY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
+++ b/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
@@ -9718,7 +9718,9 @@
       <c r="PW8" t="n">
         <v>60.99</v>
       </c>
-      <c r="PX8" t="inlineStr"/>
+      <c r="PX8" t="n">
+        <v>53.36</v>
+      </c>
       <c r="PY8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -10929,7 +10931,9 @@
       <c r="PW9" t="n">
         <v>6.23</v>
       </c>
-      <c r="PX9" t="inlineStr"/>
+      <c r="PX9" t="n">
+        <v>5.99</v>
+      </c>
       <c r="PY9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -12140,7 +12144,9 @@
       <c r="PW10" t="n">
         <v>0.11</v>
       </c>
-      <c r="PX10" t="inlineStr"/>
+      <c r="PX10" t="n">
+        <v>0.13</v>
+      </c>
       <c r="PY10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -13351,7 +13357,9 @@
       <c r="PW11" t="n">
         <v>0.57</v>
       </c>
-      <c r="PX11" t="inlineStr"/>
+      <c r="PX11" t="n">
+        <v>0.52</v>
+      </c>
       <c r="PY11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -15099,7 +15107,9 @@
       <c r="PW13" t="n">
         <v>28.28</v>
       </c>
-      <c r="PX13" t="inlineStr"/>
+      <c r="PX13" t="n">
+        <v>27.82</v>
+      </c>
       <c r="PY13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -16310,7 +16320,9 @@
       <c r="PW14" t="n">
         <v>3.67</v>
       </c>
-      <c r="PX14" t="inlineStr"/>
+      <c r="PX14" t="n">
+        <v>3.06</v>
+      </c>
       <c r="PY14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -17521,7 +17533,9 @@
       <c r="PW15" t="n">
         <v>22.92</v>
       </c>
-      <c r="PX15" t="inlineStr"/>
+      <c r="PX15" t="n">
+        <v>21.02</v>
+      </c>
       <c r="PY15" t="inlineStr"/>
     </row>
   </sheetData>

--- a/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
+++ b/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
@@ -3829,7 +3829,9 @@
       <c r="PX2" t="n">
         <v>4.27</v>
       </c>
-      <c r="PY2" t="inlineStr"/>
+      <c r="PY2" t="n">
+        <v>4.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5042,7 +5044,9 @@
       <c r="PX3" t="n">
         <v>295.75</v>
       </c>
-      <c r="PY3" t="inlineStr"/>
+      <c r="PY3" t="n">
+        <v>337.13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6255,7 +6259,9 @@
       <c r="PX4" t="n">
         <v>3.48</v>
       </c>
-      <c r="PY4" t="inlineStr"/>
+      <c r="PY4" t="n">
+        <v>3.45</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">

--- a/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
+++ b/services/data_raw/eurostat/AT_milk_apro_mk_colm.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PY15"/>
+  <dimension ref="A1:QB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2615,6 +2615,21 @@
       <c r="PY1" t="inlineStr">
         <is>
           <t>2026-03</t>
+        </is>
+      </c>
+      <c r="PZ1" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="QA1" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="QB1" t="inlineStr">
+        <is>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -3832,6 +3847,15 @@
       <c r="PY2" t="n">
         <v>4.21</v>
       </c>
+      <c r="PZ2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>4.07</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5047,6 +5071,15 @@
       <c r="PY3" t="n">
         <v>337.13</v>
       </c>
+      <c r="PZ3" t="n">
+        <v>331.39</v>
+      </c>
+      <c r="QA3" t="n">
+        <v>341.57</v>
+      </c>
+      <c r="QB3" t="n">
+        <v>308.18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6261,6 +6294,15 @@
       </c>
       <c r="PY4" t="n">
         <v>3.45</v>
+      </c>
+      <c r="PZ4" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="QA4" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="QB4" t="n">
+        <v>3.37</v>
       </c>
     </row>
     <row r="5">
@@ -7013,6 +7055,9 @@
       <c r="PW5" t="inlineStr"/>
       <c r="PX5" t="inlineStr"/>
       <c r="PY5" t="inlineStr"/>
+      <c r="PZ5" t="inlineStr"/>
+      <c r="QA5" t="inlineStr"/>
+      <c r="QB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7764,6 +7809,9 @@
       <c r="PW6" t="inlineStr"/>
       <c r="PX6" t="inlineStr"/>
       <c r="PY6" t="inlineStr"/>
+      <c r="PZ6" t="inlineStr"/>
+      <c r="QA6" t="inlineStr"/>
+      <c r="QB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8515,6 +8563,9 @@
       <c r="PW7" t="inlineStr"/>
       <c r="PX7" t="inlineStr"/>
       <c r="PY7" t="inlineStr"/>
+      <c r="PZ7" t="inlineStr"/>
+      <c r="QA7" t="inlineStr"/>
+      <c r="QB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -9722,12 +9773,21 @@
         <v>61.24</v>
       </c>
       <c r="PW8" t="n">
-        <v>60.99</v>
+        <v>61.77</v>
       </c>
       <c r="PX8" t="n">
-        <v>53.36</v>
-      </c>
-      <c r="PY8" t="inlineStr"/>
+        <v>54.14</v>
+      </c>
+      <c r="PY8" t="n">
+        <v>60.98</v>
+      </c>
+      <c r="PZ8" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="QA8" t="n">
+        <v>57.74</v>
+      </c>
+      <c r="QB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10935,12 +10995,21 @@
         <v>7.05</v>
       </c>
       <c r="PW9" t="n">
-        <v>6.23</v>
+        <v>6.4</v>
       </c>
       <c r="PX9" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="PY9" t="inlineStr"/>
+        <v>6.17</v>
+      </c>
+      <c r="PY9" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="PZ9" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="QA9" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="QB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -12121,7 +12190,7 @@
         <v>0.06</v>
       </c>
       <c r="PN10" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="PO10" t="n">
         <v>0.15</v>
@@ -12130,7 +12199,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="PQ10" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="PR10" t="n">
         <v>0.13</v>
@@ -12153,7 +12222,16 @@
       <c r="PX10" t="n">
         <v>0.13</v>
       </c>
-      <c r="PY10" t="inlineStr"/>
+      <c r="PY10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="PZ10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="QA10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="QB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13334,16 +13412,16 @@
         <v>0.37</v>
       </c>
       <c r="PN11" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="PO11" t="n">
-        <v>0.31</v>
+        <v>0.45</v>
       </c>
       <c r="PP11" t="n">
         <v>0.37</v>
       </c>
       <c r="PQ11" t="n">
-        <v>0.28</v>
+        <v>0.42</v>
       </c>
       <c r="PR11" t="n">
         <v>0.46</v>
@@ -13366,7 +13444,16 @@
       <c r="PX11" t="n">
         <v>0.52</v>
       </c>
-      <c r="PY11" t="inlineStr"/>
+      <c r="PY11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="PZ11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="QA11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="QB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13952,6 +14039,9 @@
       <c r="PW12" t="inlineStr"/>
       <c r="PX12" t="inlineStr"/>
       <c r="PY12" t="inlineStr"/>
+      <c r="PZ12" t="inlineStr"/>
+      <c r="QA12" t="inlineStr"/>
+      <c r="QB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15114,9 +15204,18 @@
         <v>28.28</v>
       </c>
       <c r="PX13" t="n">
-        <v>27.82</v>
-      </c>
-      <c r="PY13" t="inlineStr"/>
+        <v>28.53</v>
+      </c>
+      <c r="PY13" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="PZ13" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="QA13" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="QB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -16327,9 +16426,18 @@
         <v>3.67</v>
       </c>
       <c r="PX14" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="PY14" t="inlineStr"/>
+        <v>3.07</v>
+      </c>
+      <c r="PY14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="PZ14" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="QA14" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="QB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17537,12 +17645,21 @@
         <v>21.96</v>
       </c>
       <c r="PW15" t="n">
-        <v>22.92</v>
+        <v>23.13</v>
       </c>
       <c r="PX15" t="n">
-        <v>21.02</v>
-      </c>
-      <c r="PY15" t="inlineStr"/>
+        <v>21.86</v>
+      </c>
+      <c r="PY15" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="PZ15" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="QA15" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="QB15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
